--- a/public/data/seguimiento PeYa.xlsx
+++ b/public/data/seguimiento PeYa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTOSO\Desktop\PeYa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA242583-EF1F-4D5B-942B-C10BDD21570C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E12B4D-8FB1-4637-8246-88850ABFCEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{91F2F213-BFE5-4952-859F-23AD74A1FBA0}"/>
   </bookViews>
@@ -1262,27 +1262,45 @@
       <c r="A56" s="2">
         <v>46247</v>
       </c>
+      <c r="B56" s="1">
+        <v>166</v>
+      </c>
+      <c r="C56" s="1">
+        <v>37</v>
+      </c>
       <c r="D56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>46248</v>
       </c>
+      <c r="B57" s="1">
+        <v>166</v>
+      </c>
+      <c r="C57" s="1">
+        <v>37</v>
+      </c>
       <c r="D57">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>46249</v>
       </c>
+      <c r="B58" s="1">
+        <v>166</v>
+      </c>
+      <c r="C58" s="1">
+        <v>37</v>
+      </c>
       <c r="D58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
